--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2085,6 +2085,3479 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131602639</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91789</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>576440</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6712349</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131602638</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91789</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>576425</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6712404</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131602641</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57084</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>576507</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6712301</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131602652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Skeletocutis odora</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sacc.) Ginns</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>576394</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6712499</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131602672</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>576430</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6712487</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131602666</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99031</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>576425</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6712294</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131602642</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57084</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>576501</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6712292</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131602640</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57084</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>576509</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6712307</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131602671</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>576477</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6712385</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131602634</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>576497</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6712331</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131602651</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97896</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>576480</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6712386</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131602645</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>576433</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6712311</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131602678</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57893</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>576433</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6712485</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131602664</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99031</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>576466</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6712359</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131602643</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57084</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>576438</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6712296</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131602644</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>576455</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6712469</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131602661</v>
+      </c>
+      <c r="B30" t="n">
+        <v>81243</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>576458</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6712292</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131602670</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92249</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>576464</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6712461</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131602665</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99031</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>576466</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6712350</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131602675</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>576432</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6712316</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131602636</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97271</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>576455</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6712254</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131602633</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>576404</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6712286</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131602637</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91789</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>576497</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6712294</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131602674</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>576481</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6712402</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131602646</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>576411</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6712267</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131602676</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>576425</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6712244</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131602668</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>576500</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6712336</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>födosök</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131602650</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>576438</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6712476</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131602673</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8442</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>576455</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6712458</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131602647</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>576406</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6712290</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131602635</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97271</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>53</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>576455</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6712468</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>131602639</v>
       </c>
       <c r="B14" t="n">
-        <v>91789</v>
+        <v>91791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131602638</v>
+        <v>131602641</v>
       </c>
       <c r="B15" t="n">
-        <v>91789</v>
+        <v>57086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,34 +2205,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576425</v>
+        <v>576507</v>
       </c>
       <c r="R15" t="n">
-        <v>6712404</v>
+        <v>6712301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2274,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131602641</v>
+        <v>131602638</v>
       </c>
       <c r="B16" t="n">
-        <v>57084</v>
+        <v>91791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,39 +2317,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576507</v>
+        <v>576425</v>
       </c>
       <c r="R16" t="n">
-        <v>6712301</v>
+        <v>6712404</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92208</v>
+        <v>92210</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>131602666</v>
       </c>
       <c r="B19" t="n">
-        <v>99031</v>
+        <v>99033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602642</v>
+        <v>131602651</v>
       </c>
       <c r="B20" t="n">
-        <v>57084</v>
+        <v>97898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,39 +2759,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576501</v>
+        <v>576480</v>
       </c>
       <c r="R20" t="n">
-        <v>6712292</v>
+        <v>6712386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,7 +2858,7 @@
         <v>131602640</v>
       </c>
       <c r="B21" t="n">
-        <v>57084</v>
+        <v>57086</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,10 +2967,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602671</v>
+        <v>131602642</v>
       </c>
       <c r="B22" t="n">
-        <v>8442</v>
+        <v>57086</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,27 +2978,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576477</v>
+        <v>576501</v>
       </c>
       <c r="R22" t="n">
-        <v>6712385</v>
+        <v>6712292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3052,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602634</v>
+        <v>131602671</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>8442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,21 +3090,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576497</v>
+        <v>576477</v>
       </c>
       <c r="R23" t="n">
-        <v>6712331</v>
+        <v>6712385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602651</v>
+        <v>131602634</v>
       </c>
       <c r="B24" t="n">
-        <v>97896</v>
+        <v>5197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,34 +3202,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576480</v>
+        <v>576497</v>
       </c>
       <c r="R24" t="n">
-        <v>6712386</v>
+        <v>6712331</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,38 +3415,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B26" t="n">
-        <v>57893</v>
+        <v>99033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3455,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R26" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,42 +3531,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B27" t="n">
-        <v>99031</v>
+        <v>57895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R27" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131602643</v>
+        <v>131602644</v>
       </c>
       <c r="B28" t="n">
-        <v>57084</v>
+        <v>4773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,27 +3654,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576438</v>
+        <v>576455</v>
       </c>
       <c r="R28" t="n">
-        <v>6712296</v>
+        <v>6712469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131602644</v>
+        <v>131602643</v>
       </c>
       <c r="B29" t="n">
-        <v>4773</v>
+        <v>57086</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,27 +3766,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576455</v>
+        <v>576438</v>
       </c>
       <c r="R29" t="n">
-        <v>6712469</v>
+        <v>6712296</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,7 +3870,7 @@
         <v>131602661</v>
       </c>
       <c r="B30" t="n">
-        <v>81243</v>
+        <v>81245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>131602670</v>
       </c>
       <c r="B31" t="n">
-        <v>92249</v>
+        <v>92251</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>131602665</v>
       </c>
       <c r="B32" t="n">
-        <v>99031</v>
+        <v>99033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4333,45 +4333,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602636</v>
+        <v>131602674</v>
       </c>
       <c r="B34" t="n">
-        <v>97271</v>
+        <v>5177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576455</v>
+        <v>576481</v>
       </c>
       <c r="R34" t="n">
-        <v>6712254</v>
+        <v>6712402</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4557,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602637</v>
+        <v>131602636</v>
       </c>
       <c r="B36" t="n">
-        <v>91789</v>
+        <v>97273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576497</v>
+        <v>576455</v>
       </c>
       <c r="R36" t="n">
-        <v>6712294</v>
+        <v>6712254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4627,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4637,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4664,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602674</v>
+        <v>131602637</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>91791</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,39 +4675,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576481</v>
+        <v>576497</v>
       </c>
       <c r="R37" t="n">
-        <v>6712402</v>
+        <v>6712294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,38 +4771,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602646</v>
+        <v>131602668</v>
       </c>
       <c r="B38" t="n">
-        <v>4773</v>
+        <v>57898</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576411</v>
+        <v>576500</v>
       </c>
       <c r="R38" t="n">
-        <v>6712267</v>
+        <v>6712336</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,14 +4856,19 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4995,38 +5000,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602668</v>
+        <v>131602646</v>
       </c>
       <c r="B40" t="n">
-        <v>57896</v>
+        <v>4773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576500</v>
+        <v>576411</v>
       </c>
       <c r="R40" t="n">
-        <v>6712336</v>
+        <v>6712267</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5070,7 +5075,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,19 +5085,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5115,7 +5115,7 @@
         <v>131602650</v>
       </c>
       <c r="B41" t="n">
-        <v>57896</v>
+        <v>57898</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602673</v>
+        <v>131602647</v>
       </c>
       <c r="B42" t="n">
-        <v>8442</v>
+        <v>4773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5240,21 +5240,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R42" t="n">
-        <v>6712458</v>
+        <v>6712290</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,50 +5341,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602647</v>
+        <v>131602635</v>
       </c>
       <c r="B43" t="n">
-        <v>4773</v>
+        <v>97273</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R43" t="n">
-        <v>6712290</v>
+        <v>6712468</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5416,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5426,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5453,35 +5448,40 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131602635</v>
+        <v>131602673</v>
       </c>
       <c r="B44" t="n">
-        <v>97271</v>
+        <v>8442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
@@ -5491,7 +5491,7 @@
         <v>576455</v>
       </c>
       <c r="R44" t="n">
-        <v>6712468</v>
+        <v>6712458</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -3415,42 +3415,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B26" t="n">
-        <v>99033</v>
+        <v>57895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3459,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R26" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3494,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3504,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,38 +3527,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B27" t="n">
-        <v>57895</v>
+        <v>99033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R27" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4333,50 +4333,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602674</v>
+        <v>131602636</v>
       </c>
       <c r="B34" t="n">
-        <v>5177</v>
+        <v>97273</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576481</v>
+        <v>576455</v>
       </c>
       <c r="R34" t="n">
-        <v>6712402</v>
+        <v>6712254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,10 +4440,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602633</v>
+        <v>131602637</v>
       </c>
       <c r="B35" t="n">
-        <v>5197</v>
+        <v>91791</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,39 +4451,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576404</v>
+        <v>576497</v>
       </c>
       <c r="R35" t="n">
-        <v>6712286</v>
+        <v>6712294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4520,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4530,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4557,45 +4547,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602636</v>
+        <v>131602674</v>
       </c>
       <c r="B36" t="n">
-        <v>97273</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576455</v>
+        <v>576481</v>
       </c>
       <c r="R36" t="n">
-        <v>6712254</v>
+        <v>6712402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4627,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4637,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4664,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602637</v>
+        <v>131602633</v>
       </c>
       <c r="B37" t="n">
-        <v>91791</v>
+        <v>5197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4675,34 +4670,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576497</v>
+        <v>576404</v>
       </c>
       <c r="R37" t="n">
-        <v>6712294</v>
+        <v>6712286</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131602641</v>
+        <v>131602638</v>
       </c>
       <c r="B15" t="n">
-        <v>57086</v>
+        <v>91791</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,39 +2205,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576507</v>
+        <v>576425</v>
       </c>
       <c r="R15" t="n">
-        <v>6712301</v>
+        <v>6712404</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2264,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2274,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131602638</v>
+        <v>131602641</v>
       </c>
       <c r="B16" t="n">
-        <v>91791</v>
+        <v>57086</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,34 +2312,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576425</v>
+        <v>576507</v>
       </c>
       <c r="R16" t="n">
-        <v>6712404</v>
+        <v>6712301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2520,38 +2520,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B18" t="n">
-        <v>8442</v>
+        <v>99033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R18" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,42 +2636,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B19" t="n">
-        <v>99033</v>
+        <v>8442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R19" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602651</v>
+        <v>131602642</v>
       </c>
       <c r="B20" t="n">
-        <v>97898</v>
+        <v>57086</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,34 +2759,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576480</v>
+        <v>576501</v>
       </c>
       <c r="R20" t="n">
-        <v>6712386</v>
+        <v>6712292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2967,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602642</v>
+        <v>131602671</v>
       </c>
       <c r="B22" t="n">
-        <v>57086</v>
+        <v>8442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,27 +2983,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576501</v>
+        <v>576477</v>
       </c>
       <c r="R22" t="n">
-        <v>6712292</v>
+        <v>6712385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602671</v>
+        <v>131602634</v>
       </c>
       <c r="B23" t="n">
-        <v>8442</v>
+        <v>5197</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3090,21 +3095,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576477</v>
+        <v>576497</v>
       </c>
       <c r="R23" t="n">
-        <v>6712385</v>
+        <v>6712331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602634</v>
+        <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>5197</v>
+        <v>97898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,39 +3207,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576497</v>
+        <v>576480</v>
       </c>
       <c r="R24" t="n">
-        <v>6712331</v>
+        <v>6712386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3643,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131602644</v>
+        <v>131602643</v>
       </c>
       <c r="B28" t="n">
-        <v>4773</v>
+        <v>57086</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,27 +3654,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576455</v>
+        <v>576438</v>
       </c>
       <c r="R28" t="n">
-        <v>6712469</v>
+        <v>6712296</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131602643</v>
+        <v>131602644</v>
       </c>
       <c r="B29" t="n">
-        <v>57086</v>
+        <v>4773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,27 +3766,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576438</v>
+        <v>576455</v>
       </c>
       <c r="R29" t="n">
-        <v>6712296</v>
+        <v>6712469</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3974,48 +3974,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602670</v>
+        <v>131602665</v>
       </c>
       <c r="B31" t="n">
-        <v>92251</v>
+        <v>99033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576464</v>
+        <v>576466</v>
       </c>
       <c r="R31" t="n">
-        <v>6712461</v>
+        <v>6712350</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4047,7 +4053,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +4063,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,24 +4077,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4100,54 +4095,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602665</v>
+        <v>131602670</v>
       </c>
       <c r="B32" t="n">
-        <v>99033</v>
+        <v>92251</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576466</v>
+        <v>576464</v>
       </c>
       <c r="R32" t="n">
-        <v>6712350</v>
+        <v>6712461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4168,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,12 +4178,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På rotvälta</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4203,8 +4187,24 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4333,45 +4333,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602636</v>
+        <v>131602633</v>
       </c>
       <c r="B34" t="n">
-        <v>97273</v>
+        <v>5197</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576455</v>
+        <v>576404</v>
       </c>
       <c r="R34" t="n">
-        <v>6712254</v>
+        <v>6712286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,32 +4445,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602637</v>
+        <v>131602636</v>
       </c>
       <c r="B35" t="n">
-        <v>91791</v>
+        <v>97273</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4475,10 +4480,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576497</v>
+        <v>576455</v>
       </c>
       <c r="R35" t="n">
-        <v>6712294</v>
+        <v>6712254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,10 +4552,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602674</v>
+        <v>131602637</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>91791</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4558,39 +4563,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576481</v>
+        <v>576497</v>
       </c>
       <c r="R36" t="n">
-        <v>6712402</v>
+        <v>6712294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602633</v>
+        <v>131602674</v>
       </c>
       <c r="B37" t="n">
-        <v>5197</v>
+        <v>5177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,21 +4670,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576404</v>
+        <v>576481</v>
       </c>
       <c r="R37" t="n">
-        <v>6712286</v>
+        <v>6712402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,38 +4771,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602668</v>
+        <v>131602646</v>
       </c>
       <c r="B38" t="n">
-        <v>57898</v>
+        <v>4773</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576500</v>
+        <v>576411</v>
       </c>
       <c r="R38" t="n">
-        <v>6712336</v>
+        <v>6712267</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,19 +4856,14 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -5000,38 +4995,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602646</v>
+        <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>4773</v>
+        <v>57898</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576411</v>
+        <v>576500</v>
       </c>
       <c r="R40" t="n">
-        <v>6712267</v>
+        <v>6712336</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5075,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5085,14 +5080,19 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -3974,54 +3974,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602665</v>
+        <v>131602670</v>
       </c>
       <c r="B31" t="n">
-        <v>99033</v>
+        <v>92251</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576466</v>
+        <v>576464</v>
       </c>
       <c r="R31" t="n">
-        <v>6712350</v>
+        <v>6712461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,7 +4047,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4063,12 +4057,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På rotvälta</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4077,8 +4066,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4095,48 +4100,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602670</v>
+        <v>131602665</v>
       </c>
       <c r="B32" t="n">
-        <v>92251</v>
+        <v>99033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576464</v>
+        <v>576466</v>
       </c>
       <c r="R32" t="n">
-        <v>6712461</v>
+        <v>6712350</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4168,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,7 +4189,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4187,24 +4203,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4333,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602633</v>
+        <v>131602637</v>
       </c>
       <c r="B34" t="n">
-        <v>5197</v>
+        <v>91791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,39 +4344,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576404</v>
+        <v>576497</v>
       </c>
       <c r="R34" t="n">
-        <v>6712286</v>
+        <v>6712294</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,45 +4440,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602636</v>
+        <v>131602674</v>
       </c>
       <c r="B35" t="n">
-        <v>97273</v>
+        <v>5177</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576455</v>
+        <v>576481</v>
       </c>
       <c r="R35" t="n">
-        <v>6712254</v>
+        <v>6712402</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602637</v>
+        <v>131602636</v>
       </c>
       <c r="B36" t="n">
-        <v>91791</v>
+        <v>97273</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576497</v>
+        <v>576455</v>
       </c>
       <c r="R36" t="n">
-        <v>6712294</v>
+        <v>6712254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602674</v>
+        <v>131602633</v>
       </c>
       <c r="B37" t="n">
-        <v>5177</v>
+        <v>5197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,21 +4670,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576481</v>
+        <v>576404</v>
       </c>
       <c r="R37" t="n">
-        <v>6712402</v>
+        <v>6712286</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131602638</v>
+        <v>131602641</v>
       </c>
       <c r="B15" t="n">
-        <v>91791</v>
+        <v>57086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,34 +2205,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576425</v>
+        <v>576507</v>
       </c>
       <c r="R15" t="n">
-        <v>6712404</v>
+        <v>6712301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,7 +2269,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2274,7 +2279,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,10 +2306,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131602641</v>
+        <v>131602638</v>
       </c>
       <c r="B16" t="n">
-        <v>57086</v>
+        <v>91791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,39 +2317,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576507</v>
+        <v>576425</v>
       </c>
       <c r="R16" t="n">
-        <v>6712301</v>
+        <v>6712404</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,42 +2520,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B18" t="n">
-        <v>99033</v>
+        <v>8442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R18" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,38 +2632,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B19" t="n">
-        <v>8442</v>
+        <v>99034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R19" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3199,7 +3199,7 @@
         <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>131602664</v>
       </c>
       <c r="B27" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131602643</v>
+        <v>131602644</v>
       </c>
       <c r="B28" t="n">
-        <v>57086</v>
+        <v>4773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,27 +3654,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576438</v>
+        <v>576455</v>
       </c>
       <c r="R28" t="n">
-        <v>6712296</v>
+        <v>6712469</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131602644</v>
+        <v>131602643</v>
       </c>
       <c r="B29" t="n">
-        <v>4773</v>
+        <v>57086</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,27 +3766,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576455</v>
+        <v>576438</v>
       </c>
       <c r="R29" t="n">
-        <v>6712469</v>
+        <v>6712296</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,7 +3977,7 @@
         <v>131602670</v>
       </c>
       <c r="B31" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>131602665</v>
       </c>
       <c r="B32" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4440,50 +4440,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602674</v>
+        <v>131602636</v>
       </c>
       <c r="B35" t="n">
-        <v>5177</v>
+        <v>97274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576481</v>
+        <v>576455</v>
       </c>
       <c r="R35" t="n">
-        <v>6712402</v>
+        <v>6712254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4552,45 +4547,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602636</v>
+        <v>131602674</v>
       </c>
       <c r="B36" t="n">
-        <v>97273</v>
+        <v>5177</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576455</v>
+        <v>576481</v>
       </c>
       <c r="R36" t="n">
-        <v>6712254</v>
+        <v>6712402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5229,50 +5229,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602647</v>
+        <v>131602635</v>
       </c>
       <c r="B42" t="n">
-        <v>4773</v>
+        <v>97274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R42" t="n">
-        <v>6712290</v>
+        <v>6712468</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5304,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5314,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,35 +5336,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602635</v>
+        <v>131602673</v>
       </c>
       <c r="B43" t="n">
-        <v>97273</v>
+        <v>8442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
@@ -5379,7 +5379,7 @@
         <v>576455</v>
       </c>
       <c r="R43" t="n">
-        <v>6712468</v>
+        <v>6712458</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5448,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131602673</v>
+        <v>131602647</v>
       </c>
       <c r="B44" t="n">
-        <v>8442</v>
+        <v>4773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R44" t="n">
-        <v>6712458</v>
+        <v>6712290</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>131602639</v>
       </c>
       <c r="B14" t="n">
-        <v>91791</v>
+        <v>91792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131602641</v>
+        <v>131602638</v>
       </c>
       <c r="B15" t="n">
-        <v>57086</v>
+        <v>91792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,39 +2205,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576507</v>
+        <v>576425</v>
       </c>
       <c r="R15" t="n">
-        <v>6712301</v>
+        <v>6712404</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2269,7 +2264,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2279,7 +2274,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131602638</v>
+        <v>131602641</v>
       </c>
       <c r="B16" t="n">
-        <v>91791</v>
+        <v>57087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,34 +2312,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576425</v>
+        <v>576507</v>
       </c>
       <c r="R16" t="n">
-        <v>6712404</v>
+        <v>6712301</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,38 +2520,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B18" t="n">
-        <v>8442</v>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R18" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,42 +2636,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B19" t="n">
-        <v>99034</v>
+        <v>8443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R19" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,7 +2751,7 @@
         <v>131602642</v>
       </c>
       <c r="B20" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>131602640</v>
       </c>
       <c r="B21" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602671</v>
+        <v>131602634</v>
       </c>
       <c r="B22" t="n">
-        <v>8442</v>
+        <v>5198</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576477</v>
+        <v>576497</v>
       </c>
       <c r="R22" t="n">
-        <v>6712385</v>
+        <v>6712331</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602634</v>
+        <v>131602671</v>
       </c>
       <c r="B23" t="n">
-        <v>5197</v>
+        <v>8443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576497</v>
+        <v>576477</v>
       </c>
       <c r="R23" t="n">
-        <v>6712331</v>
+        <v>6712385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,7 +3199,7 @@
         <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>131602645</v>
       </c>
       <c r="B25" t="n">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>131602678</v>
       </c>
       <c r="B26" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
         <v>131602664</v>
       </c>
       <c r="B27" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131602644</v>
+        <v>131602643</v>
       </c>
       <c r="B28" t="n">
-        <v>4773</v>
+        <v>57087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,27 +3654,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100299</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3683,10 +3683,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576455</v>
+        <v>576438</v>
       </c>
       <c r="R28" t="n">
-        <v>6712469</v>
+        <v>6712296</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131602643</v>
+        <v>131602644</v>
       </c>
       <c r="B29" t="n">
-        <v>57086</v>
+        <v>4774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,27 +3766,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3795,10 +3795,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576438</v>
+        <v>576455</v>
       </c>
       <c r="R29" t="n">
-        <v>6712296</v>
+        <v>6712469</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,7 +3870,7 @@
         <v>131602661</v>
       </c>
       <c r="B30" t="n">
-        <v>81245</v>
+        <v>81246</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,48 +3974,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602670</v>
+        <v>131602665</v>
       </c>
       <c r="B31" t="n">
-        <v>92252</v>
+        <v>99035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576464</v>
+        <v>576466</v>
       </c>
       <c r="R31" t="n">
-        <v>6712461</v>
+        <v>6712350</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4047,7 +4053,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +4063,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,24 +4077,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4100,54 +4095,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602665</v>
+        <v>131602670</v>
       </c>
       <c r="B32" t="n">
-        <v>99034</v>
+        <v>92253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576466</v>
+        <v>576464</v>
       </c>
       <c r="R32" t="n">
-        <v>6712350</v>
+        <v>6712461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4168,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,12 +4178,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På rotvälta</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4203,8 +4187,24 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4224,7 +4224,7 @@
         <v>131602675</v>
       </c>
       <c r="B33" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602637</v>
+        <v>131602633</v>
       </c>
       <c r="B34" t="n">
-        <v>91791</v>
+        <v>5198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,34 +4344,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576497</v>
+        <v>576404</v>
       </c>
       <c r="R34" t="n">
-        <v>6712294</v>
+        <v>6712286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,32 +4445,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B35" t="n">
-        <v>97274</v>
+        <v>91792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4475,10 +4480,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R35" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,50 +4552,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602674</v>
+        <v>131602636</v>
       </c>
       <c r="B36" t="n">
-        <v>5177</v>
+        <v>97275</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576481</v>
+        <v>576455</v>
       </c>
       <c r="R36" t="n">
-        <v>6712402</v>
+        <v>6712254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602633</v>
+        <v>131602674</v>
       </c>
       <c r="B37" t="n">
-        <v>5197</v>
+        <v>5178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,21 +4670,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576404</v>
+        <v>576481</v>
       </c>
       <c r="R37" t="n">
-        <v>6712286</v>
+        <v>6712402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4774,7 +4774,7 @@
         <v>131602646</v>
       </c>
       <c r="B38" t="n">
-        <v>4773</v>
+        <v>4774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>131602676</v>
       </c>
       <c r="B39" t="n">
-        <v>5177</v>
+        <v>5178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
         <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>131602650</v>
       </c>
       <c r="B41" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>131602635</v>
       </c>
       <c r="B42" t="n">
-        <v>97274</v>
+        <v>97275</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602673</v>
+        <v>131602647</v>
       </c>
       <c r="B43" t="n">
-        <v>8442</v>
+        <v>4774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5347,21 +5347,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5376,10 +5376,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R43" t="n">
-        <v>6712458</v>
+        <v>6712290</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5448,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131602647</v>
+        <v>131602673</v>
       </c>
       <c r="B44" t="n">
-        <v>4773</v>
+        <v>8443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R44" t="n">
-        <v>6712290</v>
+        <v>6712458</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>131602639</v>
       </c>
       <c r="B14" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
         <v>131602638</v>
       </c>
       <c r="B15" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2304,7 +2304,7 @@
         <v>131602641</v>
       </c>
       <c r="B16" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92212</v>
+        <v>92215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
         <v>131602666</v>
       </c>
       <c r="B18" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
         <v>131602642</v>
       </c>
       <c r="B20" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2863,7 +2863,7 @@
         <v>131602640</v>
       </c>
       <c r="B21" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,17 +2965,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602634</v>
+        <v>131602671</v>
       </c>
       <c r="B22" t="n">
-        <v>5198</v>
+        <v>8443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576497</v>
+        <v>576477</v>
       </c>
       <c r="R22" t="n">
-        <v>6712331</v>
+        <v>6712385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,17 +3077,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602671</v>
+        <v>131602634</v>
       </c>
       <c r="B23" t="n">
-        <v>8443</v>
+        <v>5198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576477</v>
+        <v>576497</v>
       </c>
       <c r="R23" t="n">
-        <v>6712385</v>
+        <v>6712331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,7 +3199,7 @@
         <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3408,45 +3408,49 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B26" t="n">
-        <v>57896</v>
+        <v>99038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3455,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R26" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3520,49 +3524,45 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B27" t="n">
-        <v>99035</v>
+        <v>57899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R27" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
         <v>131602643</v>
       </c>
       <c r="B28" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3870,7 +3870,7 @@
         <v>131602661</v>
       </c>
       <c r="B30" t="n">
-        <v>81246</v>
+        <v>81249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3977,7 +3977,7 @@
         <v>131602665</v>
       </c>
       <c r="B31" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
         <v>131602670</v>
       </c>
       <c r="B32" t="n">
-        <v>92253</v>
+        <v>92256</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4445,32 +4445,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602637</v>
+        <v>131602636</v>
       </c>
       <c r="B35" t="n">
-        <v>91792</v>
+        <v>97278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576497</v>
+        <v>576455</v>
       </c>
       <c r="R35" t="n">
-        <v>6712294</v>
+        <v>6712254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4545,39 +4545,39 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B36" t="n">
-        <v>97275</v>
+        <v>91795</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R36" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4998,7 +4998,7 @@
         <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5115,7 +5115,7 @@
         <v>131602650</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5232,7 +5232,7 @@
         <v>131602635</v>
       </c>
       <c r="B42" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Patric Engfeldt, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2513,49 +2513,45 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B18" t="n">
-        <v>99038</v>
+        <v>8443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R18" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2629,45 +2625,49 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B19" t="n">
-        <v>8443</v>
+        <v>99038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R19" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602642</v>
+        <v>131602651</v>
       </c>
       <c r="B20" t="n">
-        <v>57090</v>
+        <v>97903</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,39 +2759,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576501</v>
+        <v>576480</v>
       </c>
       <c r="R20" t="n">
-        <v>6712292</v>
+        <v>6712386</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2828,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,14 +2848,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602640</v>
+        <v>131602642</v>
       </c>
       <c r="B21" t="n">
         <v>57090</v>
@@ -2900,10 +2895,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576509</v>
+        <v>576501</v>
       </c>
       <c r="R21" t="n">
-        <v>6712307</v>
+        <v>6712292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2965,17 +2960,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602671</v>
+        <v>131602640</v>
       </c>
       <c r="B22" t="n">
-        <v>8443</v>
+        <v>57090</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,27 +2978,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576477</v>
+        <v>576509</v>
       </c>
       <c r="R22" t="n">
-        <v>6712385</v>
+        <v>6712307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3052,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3077,17 +3072,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602634</v>
+        <v>131602671</v>
       </c>
       <c r="B23" t="n">
-        <v>5198</v>
+        <v>8443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,21 +3090,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576497</v>
+        <v>576477</v>
       </c>
       <c r="R23" t="n">
-        <v>6712331</v>
+        <v>6712385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602651</v>
+        <v>131602634</v>
       </c>
       <c r="B24" t="n">
-        <v>97903</v>
+        <v>5198</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,34 +3202,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576480</v>
+        <v>576497</v>
       </c>
       <c r="R24" t="n">
-        <v>6712386</v>
+        <v>6712331</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3967,61 +3967,55 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602665</v>
+        <v>131602670</v>
       </c>
       <c r="B31" t="n">
-        <v>99038</v>
+        <v>92256</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576466</v>
+        <v>576464</v>
       </c>
       <c r="R31" t="n">
-        <v>6712350</v>
+        <v>6712461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,7 +4047,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4063,12 +4057,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På rotvälta</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4077,8 +4066,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4088,55 +4093,61 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602670</v>
+        <v>131602665</v>
       </c>
       <c r="B32" t="n">
-        <v>92256</v>
+        <v>99038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576464</v>
+        <v>576466</v>
       </c>
       <c r="R32" t="n">
-        <v>6712461</v>
+        <v>6712350</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4168,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,7 +4189,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4187,24 +4203,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4326,57 +4326,52 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602633</v>
+        <v>131602636</v>
       </c>
       <c r="B34" t="n">
-        <v>5198</v>
+        <v>97278</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576404</v>
+        <v>576455</v>
       </c>
       <c r="R34" t="n">
-        <v>6712286</v>
+        <v>6712254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,32 +4440,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B35" t="n">
-        <v>97278</v>
+        <v>91795</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,10 +4475,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R35" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4545,17 +4540,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602637</v>
+        <v>131602633</v>
       </c>
       <c r="B36" t="n">
-        <v>91795</v>
+        <v>5198</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4563,34 +4558,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576497</v>
+        <v>576404</v>
       </c>
       <c r="R36" t="n">
-        <v>6712294</v>
+        <v>6712286</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4764,45 +4764,45 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602646</v>
+        <v>131602668</v>
       </c>
       <c r="B38" t="n">
-        <v>4774</v>
+        <v>57902</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576411</v>
+        <v>576500</v>
       </c>
       <c r="R38" t="n">
-        <v>6712267</v>
+        <v>6712336</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,14 +4856,19 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4876,17 +4881,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131602676</v>
+        <v>131602646</v>
       </c>
       <c r="B39" t="n">
-        <v>5178</v>
+        <v>4774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,21 +4899,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4923,10 +4928,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576425</v>
+        <v>576411</v>
       </c>
       <c r="R39" t="n">
-        <v>6712244</v>
+        <v>6712267</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4958,7 +4963,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +4973,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4988,45 +4993,45 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602668</v>
+        <v>131602676</v>
       </c>
       <c r="B40" t="n">
-        <v>57902</v>
+        <v>5178</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576500</v>
+        <v>576425</v>
       </c>
       <c r="R40" t="n">
-        <v>6712336</v>
+        <v>6712244</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5070,7 +5075,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,19 +5085,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Patric Engfeldt, Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2748,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602651</v>
+        <v>131602642</v>
       </c>
       <c r="B20" t="n">
-        <v>97903</v>
+        <v>57090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,34 +2759,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576480</v>
+        <v>576501</v>
       </c>
       <c r="R20" t="n">
-        <v>6712386</v>
+        <v>6712292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2855,7 +2860,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602642</v>
+        <v>131602640</v>
       </c>
       <c r="B21" t="n">
         <v>57090</v>
@@ -2895,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576501</v>
+        <v>576509</v>
       </c>
       <c r="R21" t="n">
-        <v>6712292</v>
+        <v>6712307</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602640</v>
+        <v>131602671</v>
       </c>
       <c r="B22" t="n">
-        <v>57090</v>
+        <v>8443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2978,27 +2983,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3007,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576509</v>
+        <v>576477</v>
       </c>
       <c r="R22" t="n">
-        <v>6712307</v>
+        <v>6712385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602671</v>
+        <v>131602634</v>
       </c>
       <c r="B23" t="n">
-        <v>8443</v>
+        <v>5198</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3090,21 +3095,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576477</v>
+        <v>576497</v>
       </c>
       <c r="R23" t="n">
-        <v>6712385</v>
+        <v>6712331</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602634</v>
+        <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>5198</v>
+        <v>97903</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,39 +3207,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576497</v>
+        <v>576480</v>
       </c>
       <c r="R24" t="n">
-        <v>6712331</v>
+        <v>6712386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4333,45 +4333,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602636</v>
+        <v>131602633</v>
       </c>
       <c r="B34" t="n">
-        <v>97278</v>
+        <v>5198</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576455</v>
+        <v>576404</v>
       </c>
       <c r="R34" t="n">
-        <v>6712254</v>
+        <v>6712286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,32 +4445,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602637</v>
+        <v>131602636</v>
       </c>
       <c r="B35" t="n">
-        <v>91795</v>
+        <v>97278</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4475,10 +4480,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576497</v>
+        <v>576455</v>
       </c>
       <c r="R35" t="n">
-        <v>6712294</v>
+        <v>6712254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,10 +4552,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602633</v>
+        <v>131602674</v>
       </c>
       <c r="B36" t="n">
-        <v>5198</v>
+        <v>5178</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4558,21 +4563,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,10 +4592,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576404</v>
+        <v>576481</v>
       </c>
       <c r="R36" t="n">
-        <v>6712286</v>
+        <v>6712402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4627,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4637,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4664,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602674</v>
+        <v>131602637</v>
       </c>
       <c r="B37" t="n">
-        <v>5178</v>
+        <v>91795</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,39 +4675,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576481</v>
+        <v>576497</v>
       </c>
       <c r="R37" t="n">
-        <v>6712402</v>
+        <v>6712294</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5229,35 +5229,40 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602635</v>
+        <v>131602673</v>
       </c>
       <c r="B42" t="n">
-        <v>97278</v>
+        <v>8443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>106554</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
@@ -5267,7 +5272,7 @@
         <v>576455</v>
       </c>
       <c r="R42" t="n">
-        <v>6712468</v>
+        <v>6712458</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5304,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5314,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5336,50 +5341,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602647</v>
+        <v>131602635</v>
       </c>
       <c r="B43" t="n">
-        <v>4774</v>
+        <v>97278</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R43" t="n">
-        <v>6712290</v>
+        <v>6712468</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5448,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131602673</v>
+        <v>131602647</v>
       </c>
       <c r="B44" t="n">
-        <v>8443</v>
+        <v>4774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R44" t="n">
-        <v>6712458</v>
+        <v>6712290</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>131602639</v>
       </c>
       <c r="B14" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131602638</v>
       </c>
       <c r="B15" t="n">
-        <v>91795</v>
+        <v>91801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>131602641</v>
       </c>
       <c r="B16" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92215</v>
+        <v>92221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,38 +2520,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B18" t="n">
-        <v>8443</v>
+        <v>99044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R18" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,42 +2636,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>8443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R19" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602642</v>
+        <v>131602634</v>
       </c>
       <c r="B20" t="n">
-        <v>57090</v>
+        <v>5198</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,27 +2759,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576501</v>
+        <v>576497</v>
       </c>
       <c r="R20" t="n">
-        <v>6712292</v>
+        <v>6712331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602640</v>
+        <v>131602642</v>
       </c>
       <c r="B21" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576509</v>
+        <v>576501</v>
       </c>
       <c r="R21" t="n">
-        <v>6712307</v>
+        <v>6712292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602671</v>
+        <v>131602640</v>
       </c>
       <c r="B22" t="n">
-        <v>8443</v>
+        <v>57092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,27 +2983,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576477</v>
+        <v>576509</v>
       </c>
       <c r="R22" t="n">
-        <v>6712385</v>
+        <v>6712307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602634</v>
+        <v>131602671</v>
       </c>
       <c r="B23" t="n">
-        <v>5198</v>
+        <v>8443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576497</v>
+        <v>576477</v>
       </c>
       <c r="R23" t="n">
-        <v>6712331</v>
+        <v>6712385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,7 +3199,7 @@
         <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,42 +3415,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B26" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3459,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R26" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3494,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3504,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,38 +3527,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>99044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R27" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,7 +3646,7 @@
         <v>131602643</v>
       </c>
       <c r="B28" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>131602661</v>
       </c>
       <c r="B30" t="n">
-        <v>81249</v>
+        <v>81251</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,48 +3974,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602670</v>
+        <v>131602665</v>
       </c>
       <c r="B31" t="n">
-        <v>92256</v>
+        <v>99044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576464</v>
+        <v>576466</v>
       </c>
       <c r="R31" t="n">
-        <v>6712461</v>
+        <v>6712350</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4047,7 +4053,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4057,7 +4063,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4066,24 +4077,8 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4100,54 +4095,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602665</v>
+        <v>131602670</v>
       </c>
       <c r="B32" t="n">
-        <v>99038</v>
+        <v>92262</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576466</v>
+        <v>576464</v>
       </c>
       <c r="R32" t="n">
-        <v>6712350</v>
+        <v>6712461</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4179,7 +4168,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4189,12 +4178,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På rotvälta</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4203,8 +4187,24 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4333,50 +4333,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602633</v>
+        <v>131602636</v>
       </c>
       <c r="B34" t="n">
-        <v>5198</v>
+        <v>97284</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576404</v>
+        <v>576455</v>
       </c>
       <c r="R34" t="n">
-        <v>6712286</v>
+        <v>6712254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,32 +4440,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B35" t="n">
-        <v>97278</v>
+        <v>91801</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4480,10 +4475,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R35" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4510,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4520,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4664,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602637</v>
+        <v>131602633</v>
       </c>
       <c r="B37" t="n">
-        <v>91795</v>
+        <v>5198</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4675,34 +4670,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576497</v>
+        <v>576404</v>
       </c>
       <c r="R37" t="n">
-        <v>6712294</v>
+        <v>6712286</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4774,7 +4774,7 @@
         <v>131602668</v>
       </c>
       <c r="B38" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>131602650</v>
       </c>
       <c r="B41" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5229,40 +5229,35 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602673</v>
+        <v>131602635</v>
       </c>
       <c r="B42" t="n">
-        <v>8443</v>
+        <v>97284</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106554</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
@@ -5272,7 +5267,7 @@
         <v>576455</v>
       </c>
       <c r="R42" t="n">
-        <v>6712458</v>
+        <v>6712468</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5304,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5314,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,45 +5336,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602635</v>
+        <v>131602647</v>
       </c>
       <c r="B43" t="n">
-        <v>97278</v>
+        <v>4774</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R43" t="n">
-        <v>6712468</v>
+        <v>6712290</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5448,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131602647</v>
+        <v>131602673</v>
       </c>
       <c r="B44" t="n">
-        <v>4774</v>
+        <v>8443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,21 +5459,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100299</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R44" t="n">
-        <v>6712290</v>
+        <v>6712458</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2520,42 +2520,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B18" t="n">
-        <v>99044</v>
+        <v>8443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R18" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,38 +2632,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B19" t="n">
-        <v>8443</v>
+        <v>99044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R19" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3415,38 +3415,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B26" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3455,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R26" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,42 +3531,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B27" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R27" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4333,32 +4333,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B34" t="n">
-        <v>97284</v>
+        <v>91801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R34" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,10 +4440,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602637</v>
+        <v>131602674</v>
       </c>
       <c r="B35" t="n">
-        <v>91801</v>
+        <v>5178</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4451,34 +4451,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576497</v>
+        <v>576481</v>
       </c>
       <c r="R35" t="n">
-        <v>6712294</v>
+        <v>6712402</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4510,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4520,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4547,50 +4552,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602674</v>
+        <v>131602636</v>
       </c>
       <c r="B36" t="n">
-        <v>5178</v>
+        <v>97284</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576481</v>
+        <v>576455</v>
       </c>
       <c r="R36" t="n">
-        <v>6712402</v>
+        <v>6712254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,38 +4771,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602668</v>
+        <v>131602646</v>
       </c>
       <c r="B38" t="n">
-        <v>57904</v>
+        <v>4774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576500</v>
+        <v>576411</v>
       </c>
       <c r="R38" t="n">
-        <v>6712336</v>
+        <v>6712267</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,19 +4856,14 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4888,10 +4883,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131602646</v>
+        <v>131602676</v>
       </c>
       <c r="B39" t="n">
-        <v>4774</v>
+        <v>5178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4899,21 +4894,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4928,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576411</v>
+        <v>576425</v>
       </c>
       <c r="R39" t="n">
-        <v>6712267</v>
+        <v>6712244</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4963,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4973,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5000,38 +4995,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602676</v>
+        <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>5178</v>
+        <v>57904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576425</v>
+        <v>576500</v>
       </c>
       <c r="R40" t="n">
-        <v>6712244</v>
+        <v>6712336</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5075,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5085,14 +5080,19 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -3415,42 +3415,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B26" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3459,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R26" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3494,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3504,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,38 +3527,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B27" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R27" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4771,38 +4771,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602646</v>
+        <v>131602668</v>
       </c>
       <c r="B38" t="n">
-        <v>4774</v>
+        <v>57904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576411</v>
+        <v>576500</v>
       </c>
       <c r="R38" t="n">
-        <v>6712267</v>
+        <v>6712336</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,14 +4856,19 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4883,10 +4888,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131602676</v>
+        <v>131602646</v>
       </c>
       <c r="B39" t="n">
-        <v>5178</v>
+        <v>4774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,21 +4899,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4923,10 +4928,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576425</v>
+        <v>576411</v>
       </c>
       <c r="R39" t="n">
-        <v>6712244</v>
+        <v>6712267</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4958,7 +4963,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +4973,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4995,38 +5000,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602668</v>
+        <v>131602676</v>
       </c>
       <c r="B40" t="n">
-        <v>57904</v>
+        <v>5178</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5035,10 +5040,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576500</v>
+        <v>576425</v>
       </c>
       <c r="R40" t="n">
-        <v>6712336</v>
+        <v>6712244</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5070,7 +5075,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,19 +5085,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2520,38 +2520,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B18" t="n">
-        <v>8443</v>
+        <v>99044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R18" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,42 +2636,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B19" t="n">
-        <v>99044</v>
+        <v>8443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R19" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602642</v>
+        <v>131602671</v>
       </c>
       <c r="B21" t="n">
-        <v>57092</v>
+        <v>8443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,27 +2871,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576501</v>
+        <v>576477</v>
       </c>
       <c r="R21" t="n">
-        <v>6712292</v>
+        <v>6712385</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602640</v>
+        <v>131602651</v>
       </c>
       <c r="B22" t="n">
-        <v>57092</v>
+        <v>97909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,39 +2983,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576509</v>
+        <v>576480</v>
       </c>
       <c r="R22" t="n">
-        <v>6712307</v>
+        <v>6712386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3052,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602671</v>
+        <v>131602642</v>
       </c>
       <c r="B23" t="n">
-        <v>8443</v>
+        <v>57092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,27 +3090,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3124,10 +3119,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576477</v>
+        <v>576501</v>
       </c>
       <c r="R23" t="n">
-        <v>6712385</v>
+        <v>6712292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602651</v>
+        <v>131602640</v>
       </c>
       <c r="B24" t="n">
-        <v>97909</v>
+        <v>57092</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,34 +3202,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576480</v>
+        <v>576509</v>
       </c>
       <c r="R24" t="n">
-        <v>6712386</v>
+        <v>6712307</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4771,38 +4771,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602668</v>
+        <v>131602646</v>
       </c>
       <c r="B38" t="n">
-        <v>57904</v>
+        <v>4774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576500</v>
+        <v>576411</v>
       </c>
       <c r="R38" t="n">
-        <v>6712336</v>
+        <v>6712267</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,19 +4856,14 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4888,10 +4883,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131602646</v>
+        <v>131602676</v>
       </c>
       <c r="B39" t="n">
-        <v>4774</v>
+        <v>5178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4899,21 +4894,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4928,10 +4923,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576411</v>
+        <v>576425</v>
       </c>
       <c r="R39" t="n">
-        <v>6712267</v>
+        <v>6712244</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4963,7 +4958,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4973,7 +4968,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5000,38 +4995,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602676</v>
+        <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>5178</v>
+        <v>57904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5040,10 +5035,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576425</v>
+        <v>576500</v>
       </c>
       <c r="R40" t="n">
-        <v>6712244</v>
+        <v>6712336</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5075,7 +5070,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5085,14 +5080,19 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602671</v>
+        <v>131602642</v>
       </c>
       <c r="B21" t="n">
-        <v>8443</v>
+        <v>57092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,27 +2871,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576477</v>
+        <v>576501</v>
       </c>
       <c r="R21" t="n">
-        <v>6712385</v>
+        <v>6712292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602651</v>
+        <v>131602640</v>
       </c>
       <c r="B22" t="n">
-        <v>97909</v>
+        <v>57092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,34 +2983,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576480</v>
+        <v>576509</v>
       </c>
       <c r="R22" t="n">
-        <v>6712386</v>
+        <v>6712307</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602642</v>
+        <v>131602671</v>
       </c>
       <c r="B23" t="n">
-        <v>57092</v>
+        <v>8443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3090,27 +3095,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576501</v>
+        <v>576477</v>
       </c>
       <c r="R23" t="n">
-        <v>6712292</v>
+        <v>6712385</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,7 +3159,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3169,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602640</v>
+        <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>57092</v>
+        <v>97909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,39 +3207,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576509</v>
+        <v>576480</v>
       </c>
       <c r="R24" t="n">
-        <v>6712307</v>
+        <v>6712386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>131602639</v>
       </c>
       <c r="B14" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131602638</v>
       </c>
       <c r="B15" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>131602641</v>
       </c>
       <c r="B16" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92221</v>
+        <v>92224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,42 +2520,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B18" t="n">
-        <v>99044</v>
+        <v>8444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2564,10 +2560,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R18" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2605,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,38 +2632,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B19" t="n">
-        <v>8443</v>
+        <v>99047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R19" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602634</v>
+        <v>131602642</v>
       </c>
       <c r="B20" t="n">
-        <v>5198</v>
+        <v>57095</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,27 +2759,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576497</v>
+        <v>576501</v>
       </c>
       <c r="R20" t="n">
-        <v>6712331</v>
+        <v>6712292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602642</v>
+        <v>131602634</v>
       </c>
       <c r="B21" t="n">
-        <v>57092</v>
+        <v>5199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,27 +2871,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576501</v>
+        <v>576497</v>
       </c>
       <c r="R21" t="n">
-        <v>6712292</v>
+        <v>6712331</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602640</v>
+        <v>131602671</v>
       </c>
       <c r="B22" t="n">
-        <v>57092</v>
+        <v>8444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,27 +2983,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576509</v>
+        <v>576477</v>
       </c>
       <c r="R22" t="n">
-        <v>6712307</v>
+        <v>6712385</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3084,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602671</v>
+        <v>131602651</v>
       </c>
       <c r="B23" t="n">
-        <v>8443</v>
+        <v>97912</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,39 +3095,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576477</v>
+        <v>576480</v>
       </c>
       <c r="R23" t="n">
-        <v>6712385</v>
+        <v>6712386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3159,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602651</v>
+        <v>131602640</v>
       </c>
       <c r="B24" t="n">
-        <v>97909</v>
+        <v>57095</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3207,34 +3202,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576480</v>
+        <v>576509</v>
       </c>
       <c r="R24" t="n">
-        <v>6712386</v>
+        <v>6712307</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3306,7 +3306,7 @@
         <v>131602645</v>
       </c>
       <c r="B25" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3415,38 +3415,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B26" t="n">
-        <v>57901</v>
+        <v>99047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3455,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R26" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,42 +3531,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B27" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R27" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,7 +3646,7 @@
         <v>131602643</v>
       </c>
       <c r="B28" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>131602644</v>
       </c>
       <c r="B29" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>131602661</v>
       </c>
       <c r="B30" t="n">
-        <v>81251</v>
+        <v>81254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>131602665</v>
       </c>
       <c r="B31" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>131602670</v>
       </c>
       <c r="B32" t="n">
-        <v>92262</v>
+        <v>92265</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>131602675</v>
       </c>
       <c r="B33" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602637</v>
+        <v>131602674</v>
       </c>
       <c r="B34" t="n">
-        <v>91801</v>
+        <v>5179</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,34 +4344,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576497</v>
+        <v>576481</v>
       </c>
       <c r="R34" t="n">
-        <v>6712294</v>
+        <v>6712402</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4408,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4418,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,50 +4445,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602674</v>
+        <v>131602636</v>
       </c>
       <c r="B35" t="n">
-        <v>5178</v>
+        <v>97287</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576481</v>
+        <v>576455</v>
       </c>
       <c r="R35" t="n">
-        <v>6712402</v>
+        <v>6712254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B36" t="n">
-        <v>97284</v>
+        <v>91804</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R36" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,7 +4662,7 @@
         <v>131602633</v>
       </c>
       <c r="B37" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>131602646</v>
       </c>
       <c r="B38" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>131602676</v>
       </c>
       <c r="B39" t="n">
-        <v>5178</v>
+        <v>5179</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>131602650</v>
       </c>
       <c r="B41" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5229,45 +5229,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602635</v>
+        <v>131602647</v>
       </c>
       <c r="B42" t="n">
-        <v>97284</v>
+        <v>4775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R42" t="n">
-        <v>6712468</v>
+        <v>6712290</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5299,7 +5304,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5309,7 +5314,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5336,50 +5341,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602647</v>
+        <v>131602635</v>
       </c>
       <c r="B43" t="n">
-        <v>4774</v>
+        <v>97287</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R43" t="n">
-        <v>6712290</v>
+        <v>6712468</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5451,7 +5451,7 @@
         <v>131602673</v>
       </c>
       <c r="B44" t="n">
-        <v>8443</v>
+        <v>8444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2090,7 +2090,7 @@
         <v>131602639</v>
       </c>
       <c r="B14" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>131602638</v>
       </c>
       <c r="B15" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>131602641</v>
       </c>
       <c r="B16" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>131602652</v>
       </c>
       <c r="B17" t="n">
-        <v>92224</v>
+        <v>92229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,38 +2520,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602672</v>
+        <v>131602666</v>
       </c>
       <c r="B18" t="n">
-        <v>8444</v>
+        <v>99052</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576430</v>
+        <v>576425</v>
       </c>
       <c r="R18" t="n">
-        <v>6712487</v>
+        <v>6712294</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2632,42 +2636,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602666</v>
+        <v>131602672</v>
       </c>
       <c r="B19" t="n">
-        <v>99047</v>
+        <v>8444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576425</v>
+        <v>576430</v>
       </c>
       <c r="R19" t="n">
-        <v>6712294</v>
+        <v>6712487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602642</v>
+        <v>131602671</v>
       </c>
       <c r="B20" t="n">
-        <v>57095</v>
+        <v>8444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,27 +2759,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576501</v>
+        <v>576477</v>
       </c>
       <c r="R20" t="n">
-        <v>6712292</v>
+        <v>6712385</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602671</v>
+        <v>131602651</v>
       </c>
       <c r="B22" t="n">
-        <v>8444</v>
+        <v>97917</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,39 +2983,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576477</v>
+        <v>576480</v>
       </c>
       <c r="R22" t="n">
-        <v>6712385</v>
+        <v>6712386</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3047,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,7 +3052,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602651</v>
+        <v>131602642</v>
       </c>
       <c r="B23" t="n">
-        <v>97912</v>
+        <v>57100</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3095,34 +3090,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576480</v>
+        <v>576501</v>
       </c>
       <c r="R23" t="n">
-        <v>6712386</v>
+        <v>6712292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,7 +3194,7 @@
         <v>131602640</v>
       </c>
       <c r="B24" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3415,42 +3415,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B26" t="n">
-        <v>99047</v>
+        <v>57909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3459,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R26" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3494,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3504,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,38 +3527,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>99052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R27" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,7 +3646,7 @@
         <v>131602643</v>
       </c>
       <c r="B28" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>131602661</v>
       </c>
       <c r="B30" t="n">
-        <v>81254</v>
+        <v>81259</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3974,54 +3974,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602665</v>
+        <v>131602670</v>
       </c>
       <c r="B31" t="n">
-        <v>99047</v>
+        <v>92270</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576466</v>
+        <v>576464</v>
       </c>
       <c r="R31" t="n">
-        <v>6712350</v>
+        <v>6712461</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,7 +4047,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4063,12 +4057,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På rotvälta</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4077,8 +4066,24 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4095,48 +4100,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602670</v>
+        <v>131602665</v>
       </c>
       <c r="B32" t="n">
-        <v>92265</v>
+        <v>99052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576464</v>
+        <v>576466</v>
       </c>
       <c r="R32" t="n">
-        <v>6712461</v>
+        <v>6712350</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4168,7 +4179,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,7 +4189,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4187,24 +4203,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4333,50 +4333,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602674</v>
+        <v>131602636</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>97292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576481</v>
+        <v>576455</v>
       </c>
       <c r="R34" t="n">
-        <v>6712402</v>
+        <v>6712254</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,45 +4440,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602636</v>
+        <v>131602633</v>
       </c>
       <c r="B35" t="n">
-        <v>97287</v>
+        <v>5199</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576455</v>
+        <v>576404</v>
       </c>
       <c r="R35" t="n">
-        <v>6712254</v>
+        <v>6712286</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4555,7 +4555,7 @@
         <v>131602637</v>
       </c>
       <c r="B36" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602633</v>
+        <v>131602674</v>
       </c>
       <c r="B37" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,21 +4670,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4699,10 +4699,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576404</v>
+        <v>576481</v>
       </c>
       <c r="R37" t="n">
-        <v>6712286</v>
+        <v>6712402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4998,7 +4998,7 @@
         <v>131602668</v>
       </c>
       <c r="B40" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>131602650</v>
       </c>
       <c r="B41" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5229,50 +5229,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602647</v>
+        <v>131602635</v>
       </c>
       <c r="B42" t="n">
-        <v>4775</v>
+        <v>97292</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576406</v>
+        <v>576455</v>
       </c>
       <c r="R42" t="n">
-        <v>6712290</v>
+        <v>6712468</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5304,7 +5299,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5314,7 +5309,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,45 +5336,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602635</v>
+        <v>131602647</v>
       </c>
       <c r="B43" t="n">
-        <v>97287</v>
+        <v>4775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576455</v>
+        <v>576406</v>
       </c>
       <c r="R43" t="n">
-        <v>6712468</v>
+        <v>6712290</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -2972,10 +2972,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602651</v>
+        <v>131602642</v>
       </c>
       <c r="B22" t="n">
-        <v>97917</v>
+        <v>57100</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2983,34 +2983,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576480</v>
+        <v>576501</v>
       </c>
       <c r="R22" t="n">
-        <v>6712386</v>
+        <v>6712292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3042,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3057,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,7 +3084,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602642</v>
+        <v>131602640</v>
       </c>
       <c r="B23" t="n">
         <v>57100</v>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576501</v>
+        <v>576509</v>
       </c>
       <c r="R23" t="n">
-        <v>6712292</v>
+        <v>6712307</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,10 +3196,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602640</v>
+        <v>131602651</v>
       </c>
       <c r="B24" t="n">
-        <v>57100</v>
+        <v>97917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,39 +3207,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576509</v>
+        <v>576480</v>
       </c>
       <c r="R24" t="n">
-        <v>6712307</v>
+        <v>6712386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,38 +3415,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602678</v>
+        <v>131602664</v>
       </c>
       <c r="B26" t="n">
-        <v>57909</v>
+        <v>99052</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3455,10 +3459,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576433</v>
+        <v>576466</v>
       </c>
       <c r="R26" t="n">
-        <v>6712485</v>
+        <v>6712359</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3494,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3504,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,42 +3531,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602664</v>
+        <v>131602678</v>
       </c>
       <c r="B27" t="n">
-        <v>99052</v>
+        <v>57909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3571,10 +3571,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576466</v>
+        <v>576433</v>
       </c>
       <c r="R27" t="n">
-        <v>6712359</v>
+        <v>6712485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4333,32 +4333,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602636</v>
+        <v>131602637</v>
       </c>
       <c r="B34" t="n">
-        <v>97292</v>
+        <v>91809</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576455</v>
+        <v>576497</v>
       </c>
       <c r="R34" t="n">
-        <v>6712254</v>
+        <v>6712294</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4552,32 +4552,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602637</v>
+        <v>131602636</v>
       </c>
       <c r="B36" t="n">
-        <v>91809</v>
+        <v>97292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576497</v>
+        <v>576455</v>
       </c>
       <c r="R36" t="n">
-        <v>6712294</v>
+        <v>6712254</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1147788</v>
+        <v>57642261</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Linderåsen, Gstr</t>
+          <t>Linderåsgruvan 1, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576545</v>
+        <v>576421</v>
       </c>
       <c r="R2" t="n">
-        <v>6712372</v>
+        <v>6712223</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-08-08</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-08-08</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,79 +762,64 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog, mossa</t>
-        </is>
-      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16566589</v>
+        <v>57642262</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Linderåsen, Gstr</t>
+          <t>Linderåsgruvan 1, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576543.6524915196</v>
+        <v>576454</v>
       </c>
       <c r="R3" t="n">
-        <v>6712439.099929414</v>
+        <v>6712469</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +843,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,34 +862,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54807380</v>
+        <v>131602635</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,39 +892,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Linderåsen, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576536</v>
+        <v>576455</v>
       </c>
       <c r="R4" t="n">
-        <v>6712438</v>
+        <v>6712468</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,12 +946,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-08-11</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-08-11</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,74 +970,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54807385</v>
+        <v>131602636</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Linderåsen, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576464.9376855461</v>
+        <v>576455</v>
       </c>
       <c r="R5" t="n">
-        <v>6712477.792076253</v>
+        <v>6712254</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,22 +1053,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-08-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-08-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,72 +1077,66 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57642254</v>
+        <v>131602661</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81355</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576500.0343894336</v>
+        <v>576458</v>
       </c>
       <c r="R6" t="n">
-        <v>6712426.854475806</v>
+        <v>6712292</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,27 +1160,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,69 +1187,65 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57642252</v>
+        <v>54899272</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1435</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576467.7980737134</v>
+        <v>576515</v>
       </c>
       <c r="R7" t="n">
-        <v>6712296.226623951</v>
+        <v>6712472</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1318,27 +1269,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>2015-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,72 +1283,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57642262</v>
+        <v>131602652</v>
       </c>
       <c r="B8" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>1506</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576453.7808953912</v>
+        <v>576394</v>
       </c>
       <c r="R8" t="n">
-        <v>6712469.188341453</v>
+        <v>6712499</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,27 +1367,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,31 +1394,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57642265</v>
+        <v>131602654</v>
       </c>
       <c r="B9" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,37 +1420,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>2812</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576408.0853290305</v>
+        <v>576428</v>
       </c>
       <c r="R9" t="n">
-        <v>6712298.899924602</v>
+        <v>6712455</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,27 +1474,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,31 +1501,25 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62129473</v>
+        <v>131602655</v>
       </c>
       <c r="B10" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,43 +1527,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Linderåsgruvan1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576378.8432785947</v>
+        <v>576406</v>
       </c>
       <c r="R10" t="n">
-        <v>6712306.156609147</v>
+        <v>6712478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,22 +1581,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,36 +1607,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>äldre mossig barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>62129472</v>
+        <v>131602656</v>
       </c>
       <c r="B11" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,43 +1634,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linderåsgruvan1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576456.0586930858</v>
+        <v>576440</v>
       </c>
       <c r="R11" t="n">
-        <v>6712408.203241502</v>
+        <v>6712476</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,22 +1688,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-09-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1833,36 +1714,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>fuktig, olikåldrig barrblandskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>57642264</v>
+        <v>131602657</v>
       </c>
       <c r="B12" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,37 +1741,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>2812</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Linderåsgruvan 1, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576459.8283283612</v>
+        <v>576457</v>
       </c>
       <c r="R12" t="n">
-        <v>6712369.890619316</v>
+        <v>6712465</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1924,27 +1795,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2014-09-01</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2014-10-30</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Observatör: Tommy Pettersson</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,68 +1822,60 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AR12" t="inlineStr"/>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Tomas Troschke</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54899272</v>
+        <v>131602658</v>
       </c>
       <c r="B13" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1435</v>
+        <v>2812</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>linderåsen, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576515.3472866961</v>
+        <v>576451</v>
       </c>
       <c r="R13" t="n">
-        <v>6712471.969560188</v>
+        <v>6712373</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2044,22 +1902,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-08-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2068,29 +1926,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lena Melin</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131602639</v>
+        <v>131602660</v>
       </c>
       <c r="B14" t="n">
-        <v>91811</v>
+        <v>96410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>2812</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2122,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576440</v>
+        <v>576434</v>
       </c>
       <c r="R14" t="n">
-        <v>6712349</v>
+        <v>6712302</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2014,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,7 +2024,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,10 +2051,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131602638</v>
+        <v>57642264</v>
       </c>
       <c r="B15" t="n">
-        <v>91811</v>
+        <v>91680</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,37 +2062,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsgruvan 1, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576425</v>
+        <v>576460</v>
       </c>
       <c r="R15" t="n">
-        <v>6712404</v>
+        <v>6712370</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,22 +2116,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:24</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,25 +2138,26 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AR15" t="inlineStr"/>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131602641</v>
+        <v>62129472</v>
       </c>
       <c r="B16" t="n">
-        <v>57102</v>
+        <v>91680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,39 +2165,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>3215</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsgruvan1, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576507</v>
+        <v>576456</v>
       </c>
       <c r="R16" t="n">
-        <v>6712301</v>
+        <v>6712408</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2371,22 +2228,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,61 +2244,75 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>fuktig, olikåldrig barrblandskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131602652</v>
+        <v>1053805</v>
       </c>
       <c r="B17" t="n">
-        <v>92231</v>
+        <v>85274</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1506</v>
+        <v>3518</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576394</v>
+        <v>576360</v>
       </c>
       <c r="R17" t="n">
-        <v>6712499</v>
+        <v>6712275</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2478,22 +2339,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:55</t>
+          <t>2011-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>08:55</t>
+          <t>2011-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,26 +2355,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>gräsbevuxen skogsväg</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131602672</v>
+        <v>57642266</v>
       </c>
       <c r="B18" t="n">
-        <v>8444</v>
+        <v>87412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,42 +2387,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106554</v>
+        <v>3624</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsgruvan 1, Gstr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576430</v>
+        <v>576315</v>
       </c>
       <c r="R18" t="n">
-        <v>6712487</v>
+        <v>6712293</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,22 +2437,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:04</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,72 +2459,64 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AR18" t="inlineStr"/>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131602666</v>
+        <v>57642265</v>
       </c>
       <c r="B19" t="n">
-        <v>99054</v>
+        <v>87146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>3762</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsgruvan 1, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576425</v>
+        <v>576408</v>
       </c>
       <c r="R19" t="n">
-        <v>6712294</v>
+        <v>6712299</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,22 +2540,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2733,25 +2562,26 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
+      <c r="AR19" t="inlineStr"/>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Via Tomas Troschke</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131602651</v>
+        <v>131602670</v>
       </c>
       <c r="B20" t="n">
-        <v>97919</v>
+        <v>92370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2759,34 +2589,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576480</v>
+        <v>576464</v>
       </c>
       <c r="R20" t="n">
-        <v>6712386</v>
+        <v>6712461</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,7 +2651,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,7 +2661,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,8 +2670,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2855,53 +2704,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131602642</v>
+        <v>1147788</v>
       </c>
       <c r="B21" t="n">
-        <v>57102</v>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576501</v>
+        <v>576545</v>
       </c>
       <c r="R21" t="n">
-        <v>6712292</v>
+        <v>6712372</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,22 +2778,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2011-08-08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2011-08-08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,69 +2794,71 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Granskog, mossa</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131602640</v>
+        <v>54807380</v>
       </c>
       <c r="B22" t="n">
-        <v>57102</v>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576509</v>
+        <v>576536</v>
       </c>
       <c r="R22" t="n">
-        <v>6712307</v>
+        <v>6712438</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3037,22 +2882,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2015-08-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>08:28</t>
+          <t>2015-08-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,68 +2896,67 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131602634</v>
+        <v>67314599</v>
       </c>
       <c r="B23" t="n">
-        <v>5199</v>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576497</v>
+        <v>576580</v>
       </c>
       <c r="R23" t="n">
-        <v>6712331</v>
+        <v>6712376</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,22 +2983,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2017-08-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2017-08-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,71 +2997,69 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131602671</v>
+        <v>54807385</v>
       </c>
       <c r="B24" t="n">
-        <v>8444</v>
+        <v>93197</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106554</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>576477</v>
+        <v>576465</v>
       </c>
       <c r="R24" t="n">
-        <v>6712385</v>
+        <v>6712478</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3261,22 +3083,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2015-08-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2015-08-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,28 +3097,29 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131602645</v>
+        <v>62129473</v>
       </c>
       <c r="B25" t="n">
-        <v>4775</v>
+        <v>92869</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3314,39 +3127,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsgruvan1, Gstr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>576433</v>
+        <v>576379</v>
       </c>
       <c r="R25" t="n">
-        <v>6712311</v>
+        <v>6712306</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3373,22 +3190,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:32</t>
+          <t>2016-09-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3399,66 +3206,66 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>äldre mossig barrskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131602678</v>
+        <v>131602637</v>
       </c>
       <c r="B26" t="n">
-        <v>57911</v>
+        <v>91937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>576433</v>
+        <v>576497</v>
       </c>
       <c r="R26" t="n">
-        <v>6712485</v>
+        <v>6712294</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3490,7 +3297,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3307,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,54 +3334,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131602664</v>
+        <v>131602638</v>
       </c>
       <c r="B27" t="n">
-        <v>99054</v>
+        <v>91937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>576466</v>
+        <v>576425</v>
       </c>
       <c r="R27" t="n">
-        <v>6712359</v>
+        <v>6712404</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3606,7 +3404,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3616,7 +3414,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3643,10 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131602643</v>
+        <v>131602639</v>
       </c>
       <c r="B28" t="n">
-        <v>57102</v>
+        <v>91937</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,39 +3452,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>576438</v>
+        <v>576440</v>
       </c>
       <c r="R28" t="n">
-        <v>6712296</v>
+        <v>6712349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3718,7 +3511,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3728,7 +3521,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3755,53 +3548,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131602644</v>
+        <v>16566589</v>
       </c>
       <c r="B29" t="n">
-        <v>4775</v>
+        <v>93233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Linderåsen, Gstr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>576455</v>
+        <v>576544</v>
       </c>
       <c r="R29" t="n">
-        <v>6712469</v>
+        <v>6712439</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3825,22 +3619,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:17</t>
+          <t>2014-09-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,63 +3633,69 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Lena Melin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131602661</v>
+        <v>131602678</v>
       </c>
       <c r="B30" t="n">
-        <v>81261</v>
+        <v>57972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>576458</v>
+        <v>576433</v>
       </c>
       <c r="R30" t="n">
-        <v>6712292</v>
+        <v>6712485</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3937,7 +3727,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3947,7 +3737,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3974,42 +3764,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131602665</v>
+        <v>131602650</v>
       </c>
       <c r="B31" t="n">
-        <v>99054</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4018,10 +3804,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>576466</v>
+        <v>576438</v>
       </c>
       <c r="R31" t="n">
-        <v>6712350</v>
+        <v>6712476</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4053,7 +3839,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4063,12 +3849,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På rotvälta</t>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4095,48 +3881,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131602670</v>
+        <v>131602668</v>
       </c>
       <c r="B32" t="n">
-        <v>92272</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4217</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>576464</v>
+        <v>576500</v>
       </c>
       <c r="R32" t="n">
-        <v>6712461</v>
+        <v>6712336</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4168,7 +3956,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4178,33 +3966,22 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>födosök</t>
         </is>
       </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4221,53 +3998,60 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131602675</v>
+        <v>133057922</v>
       </c>
       <c r="B33" t="n">
-        <v>5179</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hästkällan, Gstr</t>
+          <t>Vingesbacke, Torsåker, Gstr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>576432</v>
+        <v>576460</v>
       </c>
       <c r="R33" t="n">
-        <v>6712316</v>
+        <v>6712369</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4291,22 +4075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:31</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Trummande.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4321,22 +4100,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Carina  Nordström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Carina  Nordström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131602633</v>
+        <v>131602640</v>
       </c>
       <c r="B34" t="n">
-        <v>5199</v>
+        <v>57162</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4344,27 +4123,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4373,10 +4152,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>576404</v>
+        <v>576509</v>
       </c>
       <c r="R34" t="n">
-        <v>6712286</v>
+        <v>6712307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4408,7 +4187,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4418,7 +4197,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,10 +4224,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131602637</v>
+        <v>131602641</v>
       </c>
       <c r="B35" t="n">
-        <v>91811</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4456,34 +4235,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>576497</v>
+        <v>576507</v>
       </c>
       <c r="R35" t="n">
-        <v>6712294</v>
+        <v>6712301</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,7 +4299,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4525,7 +4309,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4552,45 +4336,50 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131602636</v>
+        <v>131602642</v>
       </c>
       <c r="B36" t="n">
-        <v>97294</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>576455</v>
+        <v>576501</v>
       </c>
       <c r="R36" t="n">
-        <v>6712254</v>
+        <v>6712292</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4622,7 +4411,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4632,7 +4421,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4659,10 +4448,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131602674</v>
+        <v>131602643</v>
       </c>
       <c r="B37" t="n">
-        <v>5179</v>
+        <v>57162</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,27 +4459,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4699,10 +4488,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>576481</v>
+        <v>576438</v>
       </c>
       <c r="R37" t="n">
-        <v>6712402</v>
+        <v>6712296</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4734,7 +4523,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4744,7 +4533,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4771,10 +4560,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131602646</v>
+        <v>131602644</v>
       </c>
       <c r="B38" t="n">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4811,10 +4600,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>576411</v>
+        <v>576455</v>
       </c>
       <c r="R38" t="n">
-        <v>6712267</v>
+        <v>6712469</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4846,7 +4635,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4856,7 +4645,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,10 +4672,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131602676</v>
+        <v>131602645</v>
       </c>
       <c r="B39" t="n">
-        <v>5179</v>
+        <v>4776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4894,21 +4683,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4923,10 +4712,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>576425</v>
+        <v>576433</v>
       </c>
       <c r="R39" t="n">
-        <v>6712244</v>
+        <v>6712311</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4958,7 +4747,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4968,7 +4757,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4995,38 +4784,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131602668</v>
+        <v>131602646</v>
       </c>
       <c r="B40" t="n">
-        <v>57914</v>
+        <v>4776</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5035,10 +4824,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>576500</v>
+        <v>576411</v>
       </c>
       <c r="R40" t="n">
-        <v>6712336</v>
+        <v>6712267</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5070,7 +4859,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5080,19 +4869,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>födosök</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5112,38 +4896,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131602650</v>
+        <v>131602647</v>
       </c>
       <c r="B41" t="n">
-        <v>57914</v>
+        <v>4776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5152,10 +4936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>576438</v>
+        <v>576406</v>
       </c>
       <c r="R41" t="n">
-        <v>6712476</v>
+        <v>6712290</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5187,7 +4971,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5197,12 +4981,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:07</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5229,10 +5008,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131602647</v>
+        <v>131602674</v>
       </c>
       <c r="B42" t="n">
-        <v>4775</v>
+        <v>5181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5240,21 +5019,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5269,10 +5048,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>576406</v>
+        <v>576481</v>
       </c>
       <c r="R42" t="n">
-        <v>6712290</v>
+        <v>6712402</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5304,7 +5083,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5314,7 +5093,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5341,45 +5120,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131602635</v>
+        <v>131602675</v>
       </c>
       <c r="B43" t="n">
-        <v>97294</v>
+        <v>5181</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>576455</v>
+        <v>576432</v>
       </c>
       <c r="R43" t="n">
-        <v>6712468</v>
+        <v>6712316</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5411,7 +5195,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5421,7 +5205,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5448,10 +5232,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131602673</v>
+        <v>131602676</v>
       </c>
       <c r="B44" t="n">
-        <v>8444</v>
+        <v>5181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5459,21 +5243,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5488,10 +5272,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>576455</v>
+        <v>576425</v>
       </c>
       <c r="R44" t="n">
-        <v>6712458</v>
+        <v>6712244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5523,7 +5307,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5533,7 +5317,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5560,27 +5344,27 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133057922</v>
+        <v>131602633</v>
       </c>
       <c r="B45" t="n">
-        <v>57958</v>
+        <v>5201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5588,32 +5372,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Vingesbacke, Torsåker, Gstr</t>
+          <t>Hästkällan, Gstr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>576460</v>
+        <v>576404</v>
       </c>
       <c r="R45" t="n">
-        <v>6712369</v>
+        <v>6712286</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5637,17 +5414,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Trummande.</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5662,15 +5444,1232 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Carina  Nordström</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Carina  Nordström</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131602634</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>576497</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6712331</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131602671</v>
+      </c>
+      <c r="B47" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>576477</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6712385</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131602672</v>
+      </c>
+      <c r="B48" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>576430</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6712487</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131602673</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>576455</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6712458</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>57642252</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>576468</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6712296</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="inlineStr"/>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>57642254</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>576500</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6712427</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR51" t="inlineStr"/>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131602664</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>576466</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6712359</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131602665</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>576466</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6712350</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På rotvälta</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131602666</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>576425</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6712294</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131602651</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hästkällan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>576480</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6712386</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>57642259</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Linderåsgruvan 1, Gstr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>576317</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6712297</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2014-09-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2014-10-30</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Observatör: Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR56" t="inlineStr"/>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Via Tomas Troschke</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8217-2026 artfynd.xlsx
+++ b/artfynd/A 8217-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AZ56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642261</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642262</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602635</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602636</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602661</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54899272</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602652</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,6 +1553,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602654</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602655</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1727,6 +1777,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602656</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602657</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1941,6 +2001,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602658</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602660</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2151,6 +2221,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642264</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62129472</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,6 +2453,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1053805</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2472,6 +2557,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642266</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2575,6 +2665,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642265</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2701,6 +2796,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602670</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1147788</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54807380</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3013,6 +3123,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67314599</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3113,6 +3228,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54807385</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3224,6 +3344,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62129473</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3331,6 +3456,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602637</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3438,6 +3568,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602638</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3545,6 +3680,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602639</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3649,6 +3789,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16566589</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3761,6 +3906,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602678</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3878,6 +4028,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602650</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3995,6 +4150,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602668</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4109,6 +4269,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133057922</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4221,6 +4386,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602640</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4333,6 +4503,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602641</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4445,6 +4620,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602642</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4557,6 +4737,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602643</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4669,6 +4854,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602644</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4781,6 +4971,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602645</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4893,6 +5088,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602646</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5005,6 +5205,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602647</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5117,6 +5322,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602674</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5229,6 +5439,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602675</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5341,6 +5556,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602676</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5453,6 +5673,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602633</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5565,6 +5790,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602634</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5677,6 +5907,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602671</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5789,6 +6024,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602672</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5901,6 +6141,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602673</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6004,6 +6249,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642252</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6107,6 +6357,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642254</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6223,6 +6478,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602664</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6344,6 +6604,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602665</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6460,6 +6725,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602666</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6567,6 +6837,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131602651</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6670,8 +6945,70 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57642259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>